--- a/input/scenario_employments_furloughed.xlsx
+++ b/input/scenario_employments_furloughed.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\labsim\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62FE4D9-EAD1-475C-9571-A47862FB060E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60685E2D-11C3-354F-937C-B624938B6802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="630" windowWidth="38370" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="UK_FullFurlough" sheetId="1" r:id="rId1"/>
-    <sheet name="UK_FlexibleFurlough" sheetId="2" r:id="rId2"/>
+    <sheet name="FullFurlough" sheetId="1" r:id="rId1"/>
+    <sheet name="FlexibleFurlough" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -365,9 +365,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -378,7 +378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3</v>
       </c>
@@ -389,7 +389,7 @@
         <v>1881207</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>4</v>
       </c>
@@ -400,7 +400,7 @@
         <v>8718950</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5</v>
       </c>
@@ -411,7 +411,7 @@
         <v>8737958</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>6</v>
       </c>
@@ -422,7 +422,7 @@
         <v>7454160</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>7</v>
       </c>
@@ -433,7 +433,7 @@
         <v>4270126</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>8</v>
       </c>
@@ -444,7 +444,7 @@
         <v>2715407</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>9</v>
       </c>
@@ -455,7 +455,7 @@
         <v>1750627</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>10</v>
       </c>
@@ -466,7 +466,7 @@
         <v>1425407</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>11</v>
       </c>
@@ -477,7 +477,7 @@
         <v>2470267</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>2300536</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1</v>
       </c>
@@ -499,7 +499,7 @@
         <v>3387400</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
@@ -510,7 +510,7 @@
         <v>3392486</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3</v>
       </c>
@@ -521,7 +521,7 @@
         <v>3065790</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>4</v>
       </c>
@@ -532,7 +532,7 @@
         <v>2138380</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>5</v>
       </c>
@@ -543,7 +543,7 @@
         <v>1363065</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>6</v>
       </c>
@@ -554,7 +554,7 @@
         <v>1017377</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>7</v>
       </c>
@@ -565,7 +565,7 @@
         <v>873919</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>8</v>
       </c>
@@ -576,7 +576,7 @@
         <v>769600</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>9</v>
       </c>
@@ -587,7 +587,7 @@
         <v>662183</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>10</v>
       </c>
@@ -598,7 +598,7 @@
         <v>538294.5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>11</v>
       </c>
@@ -609,7 +609,7 @@
         <v>421304.4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>12</v>
       </c>
@@ -628,9 +628,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783520C2-72FB-487A-91F5-36547E05A28B}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -641,7 +641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3</v>
       </c>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>4</v>
       </c>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5</v>
       </c>
@@ -674,7 +674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>6</v>
       </c>
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>7</v>
       </c>
@@ -696,7 +696,7 @@
         <v>1161161</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>8</v>
       </c>
@@ -707,7 +707,7 @@
         <v>1260439</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>9</v>
       </c>
@@ -718,7 +718,7 @@
         <v>1149153</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>10</v>
       </c>
@@ -729,7 +729,7 @@
         <v>1053994</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>11</v>
       </c>
@@ -740,7 +740,7 @@
         <v>1426863</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>12</v>
       </c>
@@ -751,7 +751,7 @@
         <v>1536632</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1</v>
       </c>
@@ -762,7 +762,7 @@
         <v>1418968</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2</v>
       </c>
@@ -773,7 +773,7 @@
         <v>1334236</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3</v>
       </c>
@@ -784,7 +784,7 @@
         <v>1302307</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>4</v>
       </c>
@@ -795,7 +795,7 @@
         <v>1462367</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>5</v>
       </c>
@@ -806,7 +806,7 @@
         <v>1246265</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>6</v>
       </c>
@@ -817,7 +817,7 @@
         <v>935477</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>7</v>
       </c>
@@ -828,7 +828,7 @@
         <v>792819</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>8</v>
       </c>
@@ -839,7 +839,7 @@
         <v>625961</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>9</v>
       </c>
@@ -850,7 +850,7 @@
         <v>516703</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>10</v>
       </c>
@@ -861,7 +861,7 @@
         <v>463921.08333333302</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>11</v>
       </c>
@@ -872,7 +872,7 @@
         <v>342591.90000000299</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>12</v>
       </c>
